--- a/tools/zongce-fill/assets/本科生综测个人加分项信息统计表（空白模板）.xlsx
+++ b/tools/zongce-fill/assets/本科生综测个人加分项信息统计表（空白模板）.xlsx
@@ -436,7 +436,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="41">
+  <borders count="45">
     <border>
       <left/>
       <right/>
@@ -941,6 +941,50 @@
         <color rgb="00BF8F00"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BF8F00"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BF8F00"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BF8F00"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BF8F00"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BF8F00"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BF8F00"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BF8F00"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BF8F00"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -1091,7 +1135,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1322,6 +1366,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4836,7 +4882,7 @@
     <row r="1" ht="44" customHeight="1" s="67">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>加分项-社会实践</t>
+          <t>加分项-社会实践（上半区=社会实践；下方黄色横幅之后第32行起=大创区）</t>
         </is>
       </c>
     </row>
@@ -4912,95 +4958,95 @@
       <c r="B7" s="33" t="n"/>
       <c r="C7" s="33" t="n"/>
     </row>
-    <row r="8">
+    <row r="8" ht="6" customHeight="1" s="67">
       <c r="B8" s="33" t="n"/>
       <c r="C8" s="33" t="n"/>
     </row>
-    <row r="9">
+    <row r="9" ht="6" customHeight="1" s="67">
       <c r="B9" s="33" t="n"/>
       <c r="C9" s="33" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="6" customHeight="1" s="67">
       <c r="B10" s="33" t="n"/>
       <c r="C10" s="33" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" ht="6" customHeight="1" s="67">
       <c r="B11" s="33" t="n"/>
       <c r="C11" s="33" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="6" customHeight="1" s="67">
       <c r="B12" s="33" t="n"/>
       <c r="C12" s="33" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="6" customHeight="1" s="67">
       <c r="B13" s="33" t="n"/>
       <c r="C13" s="33" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" ht="6" customHeight="1" s="67">
       <c r="B14" s="33" t="n"/>
       <c r="C14" s="33" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="6" customHeight="1" s="67">
       <c r="B15" s="33" t="n"/>
       <c r="C15" s="33" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="6" customHeight="1" s="67">
       <c r="B16" s="33" t="n"/>
       <c r="C16" s="33" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="6" customHeight="1" s="67">
       <c r="B17" s="33" t="n"/>
       <c r="C17" s="33" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="6" customHeight="1" s="67">
       <c r="B18" s="33" t="n"/>
       <c r="C18" s="33" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" ht="6" customHeight="1" s="67">
       <c r="B19" s="33" t="n"/>
       <c r="C19" s="33" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" ht="6" customHeight="1" s="67">
       <c r="B20" s="33" t="n"/>
       <c r="C20" s="33" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="6" customHeight="1" s="67">
       <c r="B21" s="33" t="n"/>
       <c r="C21" s="33" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" ht="6" customHeight="1" s="67">
       <c r="B22" s="33" t="n"/>
       <c r="C22" s="33" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="6" customHeight="1" s="67">
       <c r="B23" s="33" t="n"/>
       <c r="C23" s="33" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="6" customHeight="1" s="67">
       <c r="B24" s="33" t="n"/>
       <c r="C24" s="33" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="6" customHeight="1" s="67">
       <c r="B25" s="33" t="n"/>
       <c r="C25" s="33" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="6" customHeight="1" s="67">
       <c r="B26" s="33" t="n"/>
       <c r="C26" s="33" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="6" customHeight="1" s="67">
       <c r="B27" s="33" t="n"/>
       <c r="C27" s="33" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="6" customHeight="1" s="67">
       <c r="B28" s="33" t="n"/>
       <c r="C28" s="33" t="n"/>
     </row>
-    <row r="29">
+    <row r="29" ht="6" customHeight="1" s="67">
       <c r="B29" s="33" t="n"/>
       <c r="C29" s="33" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" ht="6" customHeight="1" s="67">
       <c r="B30" s="33" t="n"/>
       <c r="C30" s="33" t="n"/>
     </row>
@@ -5010,10 +5056,10 @@
           <t>↓ 大创项目填报区（从下方第 32 行开始填写）：A列=项目级别（下拉选择）｜B列=留空不填｜C列=队长/队员｜D列=项目名称（注明 已结题通过/未结题）｜E列=应得分数</t>
         </is>
       </c>
-      <c r="B31" s="80" t="n"/>
-      <c r="C31" s="80" t="n"/>
-      <c r="D31" s="80" t="n"/>
-      <c r="E31" s="80" t="n"/>
+      <c r="B31" s="84" t="n"/>
+      <c r="C31" s="84" t="n"/>
+      <c r="D31" s="84" t="n"/>
+      <c r="E31" s="85" t="n"/>
     </row>
     <row r="32">
       <c r="B32" s="33" t="n"/>
